--- a/public/post/drafts/weekly-recap/2025Ruka/ladies_race2.xlsx
+++ b/public/post/drafts/weekly-recap/2025Ruka/ladies_race2.xlsx
@@ -623,13 +623,13 @@
         <v>63.5347881870618</v>
       </c>
       <c r="F2" t="n">
-        <v>60.3316933646697</v>
+        <v>68.4265339319827</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>39.6683066353303</v>
+        <v>31.5734660680173</v>
       </c>
     </row>
     <row r="3">
@@ -649,13 +649,13 @@
         <v>89.2528879462279</v>
       </c>
       <c r="F3" t="n">
-        <v>58.1902735873559</v>
+        <v>65.9977949909207</v>
       </c>
       <c r="G3" t="n">
         <v>95</v>
       </c>
       <c r="H3" t="n">
-        <v>36.8097264126441</v>
+        <v>29.0022050090793</v>
       </c>
     </row>
     <row r="4">
@@ -675,13 +675,13 @@
         <v>60.181939377675</v>
       </c>
       <c r="F4" t="n">
-        <v>61.3197221626229</v>
+        <v>69.5471288017516</v>
       </c>
       <c r="G4" t="n">
         <v>90</v>
       </c>
       <c r="H4" t="n">
-        <v>28.6802778373771</v>
+        <v>20.4528711982484</v>
       </c>
     </row>
     <row r="5">
@@ -701,13 +701,13 @@
         <v>38.6856152449727</v>
       </c>
       <c r="F5" t="n">
-        <v>89.6161383719809</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
         <v>85</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.6161383719809</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="6">
@@ -727,13 +727,13 @@
         <v>71.0456124768418</v>
       </c>
       <c r="F6" t="n">
-        <v>42.8635740341544</v>
+        <v>48.614677286875</v>
       </c>
       <c r="G6" t="n">
         <v>80</v>
       </c>
       <c r="H6" t="n">
-        <v>37.1364259658456</v>
+        <v>31.385322713125</v>
       </c>
     </row>
     <row r="7">
@@ -753,13 +753,13 @@
         <v>77.6439929212372</v>
       </c>
       <c r="F7" t="n">
-        <v>21.8101773966144</v>
+        <v>24.736498521123</v>
       </c>
       <c r="G7" t="n">
         <v>75</v>
       </c>
       <c r="H7" t="n">
-        <v>53.1898226033856</v>
+        <v>50.263501478877</v>
       </c>
     </row>
     <row r="8">
@@ -779,13 +779,13 @@
         <v>75.434804061402</v>
       </c>
       <c r="F8" t="n">
-        <v>27.2341348832597</v>
+        <v>30.8882007245109</v>
       </c>
       <c r="G8" t="n">
         <v>72</v>
       </c>
       <c r="H8" t="n">
-        <v>44.7658651167403</v>
+        <v>41.1117992754891</v>
       </c>
     </row>
     <row r="9">
@@ -805,13 +805,13 @@
         <v>67.8659111814161</v>
       </c>
       <c r="F9" t="n">
-        <v>34.1949882708212</v>
+        <v>38.7830076486352</v>
       </c>
       <c r="G9" t="n">
         <v>69</v>
       </c>
       <c r="H9" t="n">
-        <v>34.8050117291788</v>
+        <v>30.2169923513648</v>
       </c>
     </row>
     <row r="10">
@@ -831,13 +831,13 @@
         <v>90.1643058760642</v>
       </c>
       <c r="F10" t="n">
-        <v>22.730823982568</v>
+        <v>25.7806703541982</v>
       </c>
       <c r="G10" t="n">
         <v>66</v>
       </c>
       <c r="H10" t="n">
-        <v>43.269176017432</v>
+        <v>40.2193296458018</v>
       </c>
     </row>
     <row r="11">
@@ -857,13 +857,13 @@
         <v>35.4420632219076</v>
       </c>
       <c r="F11" t="n">
-        <v>56.4902418580198</v>
+        <v>64.0696661364938</v>
       </c>
       <c r="G11" t="n">
         <v>63</v>
       </c>
       <c r="H11" t="n">
-        <v>6.5097581419802</v>
+        <v>-1.06966613649379</v>
       </c>
     </row>
     <row r="12">
@@ -883,13 +883,13 @@
         <v>40.4473150072718</v>
       </c>
       <c r="F12" t="n">
-        <v>48.0838475644533</v>
+        <v>54.5353667940655</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
       </c>
       <c r="H12" t="n">
-        <v>11.9161524355467</v>
+        <v>5.4646332059345</v>
       </c>
     </row>
     <row r="13">
@@ -909,13 +909,13 @@
         <v>69.7554529174886</v>
       </c>
       <c r="F13" t="n">
-        <v>8.19060155225158</v>
+        <v>9.28955319803266</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
       </c>
       <c r="H13" t="n">
-        <v>49.8093984477484</v>
+        <v>48.7104468019673</v>
       </c>
     </row>
     <row r="14">
@@ -935,13 +935,13 @@
         <v>15.2601955250434</v>
       </c>
       <c r="F14" t="n">
-        <v>63.192212091604</v>
+        <v>71.6708549648523</v>
       </c>
       <c r="G14" t="n">
         <v>56</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.192212091604</v>
+        <v>-15.6708549648523</v>
       </c>
     </row>
     <row r="15">
@@ -961,13 +961,13 @@
         <v>53.8838138175247</v>
       </c>
       <c r="F15" t="n">
-        <v>30.6524033327357</v>
+        <v>34.7651060292055</v>
       </c>
       <c r="G15" t="n">
         <v>54</v>
       </c>
       <c r="H15" t="n">
-        <v>23.3475966672643</v>
+        <v>19.2348939707945</v>
       </c>
     </row>
     <row r="16">
@@ -987,13 +987,13 @@
         <v>61.5503512972571</v>
       </c>
       <c r="F16" t="n">
-        <v>20.9084171800726</v>
+        <v>23.7137470846144</v>
       </c>
       <c r="G16" t="n">
         <v>52</v>
       </c>
       <c r="H16" t="n">
-        <v>31.0915828199274</v>
+        <v>28.2862529153856</v>
       </c>
     </row>
     <row r="17">
@@ -1013,13 +1013,13 @@
         <v>17.1168887098772</v>
       </c>
       <c r="F17" t="n">
-        <v>47.7813210684529</v>
+        <v>54.1922496297788</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2186789315471</v>
+        <v>-4.1922496297788</v>
       </c>
     </row>
     <row r="18">
@@ -1039,13 +1039,13 @@
         <v>12.4480658152618</v>
       </c>
       <c r="F18" t="n">
-        <v>39.9664756052368</v>
+        <v>45.3288685701796</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
       </c>
       <c r="H18" t="n">
-        <v>8.0335243947632</v>
+        <v>2.6711314298204</v>
       </c>
     </row>
     <row r="19">
@@ -1065,13 +1065,13 @@
         <v>10.8885549636229</v>
       </c>
       <c r="F19" t="n">
-        <v>14.7983889200383</v>
+        <v>16.7839224312019</v>
       </c>
       <c r="G19" t="n">
         <v>46</v>
       </c>
       <c r="H19" t="n">
-        <v>31.2016110799617</v>
+        <v>29.2160775687981</v>
       </c>
     </row>
     <row r="20">
@@ -1091,13 +1091,13 @@
         <v>48.6664860551491</v>
       </c>
       <c r="F20" t="n">
-        <v>21.0736718617305</v>
+        <v>23.901174362903</v>
       </c>
       <c r="G20" t="n">
         <v>44</v>
       </c>
       <c r="H20" t="n">
-        <v>22.9263281382695</v>
+        <v>20.098825637097</v>
       </c>
     </row>
     <row r="21">
@@ -1117,13 +1117,13 @@
         <v>6.09571589754341</v>
       </c>
       <c r="F21" t="n">
-        <v>40.1256860470755</v>
+        <v>45.5094406392405</v>
       </c>
       <c r="G21" t="n">
         <v>42</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8743139529245</v>
+        <v>-3.5094406392405</v>
       </c>
     </row>
     <row r="22">
@@ -1143,13 +1143,13 @@
         <v>28.6005154818204</v>
       </c>
       <c r="F22" t="n">
-        <v>31.9731673667572</v>
+        <v>36.2630799787158</v>
       </c>
       <c r="G22" t="n">
         <v>40</v>
       </c>
       <c r="H22" t="n">
-        <v>8.0268326332428</v>
+        <v>3.7369200212842</v>
       </c>
     </row>
     <row r="23">
@@ -1169,13 +1169,13 @@
         <v>34.134210715735</v>
       </c>
       <c r="F23" t="n">
-        <v>14.2990382609457</v>
+        <v>16.2175727580405</v>
       </c>
       <c r="G23" t="n">
         <v>38</v>
       </c>
       <c r="H23" t="n">
-        <v>23.7009617390543</v>
+        <v>21.7824272419595</v>
       </c>
     </row>
     <row r="24">
@@ -1195,13 +1195,13 @@
         <v>39.6359370261785</v>
       </c>
       <c r="F24" t="n">
-        <v>14.0170157169424</v>
+        <v>15.8977106076417</v>
       </c>
       <c r="G24" t="n">
         <v>36</v>
       </c>
       <c r="H24" t="n">
-        <v>21.9829842830576</v>
+        <v>20.1022893923583</v>
       </c>
     </row>
     <row r="25">
@@ -1221,13 +1221,13 @@
         <v>-3.45293620085181</v>
       </c>
       <c r="F25" t="n">
-        <v>29.8450620444669</v>
+        <v>33.8494419234013</v>
       </c>
       <c r="G25" t="n">
         <v>34</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1549379555331</v>
+        <v>0.150558076598699</v>
       </c>
     </row>
     <row r="26">
@@ -1247,13 +1247,13 @@
         <v>31.3064946757402</v>
       </c>
       <c r="F26" t="n">
-        <v>22.4108584133833</v>
+        <v>25.4177742766002</v>
       </c>
       <c r="G26" t="n">
         <v>32</v>
       </c>
       <c r="H26" t="n">
-        <v>9.5891415866167</v>
+        <v>6.5822257233998</v>
       </c>
     </row>
     <row r="27">
@@ -1273,13 +1273,13 @@
         <v>-46.9364057813982</v>
       </c>
       <c r="F27" t="n">
-        <v>66.9969401643004</v>
+        <v>75.9860720597</v>
       </c>
       <c r="G27" t="n">
         <v>30</v>
       </c>
       <c r="H27" t="n">
-        <v>-36.9969401643004</v>
+        <v>-45.9860720597</v>
       </c>
     </row>
     <row r="28">
@@ -1299,13 +1299,13 @@
         <v>-21.000339626368</v>
       </c>
       <c r="F28" t="n">
-        <v>42.6961465391112</v>
+        <v>48.4247856638856</v>
       </c>
       <c r="G28" t="n">
         <v>28</v>
       </c>
       <c r="H28" t="n">
-        <v>-14.6961465391112</v>
+        <v>-20.4247856638856</v>
       </c>
     </row>
     <row r="29">
@@ -1325,13 +1325,13 @@
         <v>19.908463489033</v>
       </c>
       <c r="F29" t="n">
-        <v>20.9114672651301</v>
+        <v>23.7172064065237</v>
       </c>
       <c r="G29" t="n">
         <v>26</v>
       </c>
       <c r="H29" t="n">
-        <v>5.0885327348699</v>
+        <v>2.2827935934763</v>
       </c>
     </row>
     <row r="30">
@@ -1351,13 +1351,13 @@
         <v>-35.1053998077293</v>
       </c>
       <c r="F30" t="n">
-        <v>50.1804773016437</v>
+        <v>56.913306113413</v>
       </c>
       <c r="G30" t="n">
         <v>24</v>
       </c>
       <c r="H30" t="n">
-        <v>-26.1804773016437</v>
+        <v>-32.913306113413</v>
       </c>
     </row>
     <row r="31">
@@ -1377,13 +1377,13 @@
         <v>-57.7104403409023</v>
       </c>
       <c r="F31" t="n">
-        <v>35.3852507816939</v>
+        <v>40.1329703887145</v>
       </c>
       <c r="G31" t="n">
         <v>22</v>
       </c>
       <c r="H31" t="n">
-        <v>-13.3852507816939</v>
+        <v>-18.1329703887145</v>
       </c>
     </row>
     <row r="32">
@@ -1403,13 +1403,13 @@
         <v>-26.2438507861543</v>
       </c>
       <c r="F32" t="n">
-        <v>27.9384099299465</v>
+        <v>31.6869699566006</v>
       </c>
       <c r="G32" t="n">
         <v>20</v>
       </c>
       <c r="H32" t="n">
-        <v>-7.9384099299465</v>
+        <v>-11.6869699566006</v>
       </c>
     </row>
     <row r="33">
@@ -1429,13 +1429,13 @@
         <v>7.07443201278306</v>
       </c>
       <c r="F33" t="n">
-        <v>18.7340937103877</v>
+        <v>21.2476896879124</v>
       </c>
       <c r="G33" t="n">
         <v>19</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2659062896123</v>
+        <v>-2.2476896879124</v>
       </c>
     </row>
     <row r="34">
@@ -1477,13 +1477,13 @@
         <v>-3.67646524330689</v>
       </c>
       <c r="F35" t="n">
-        <v>4.39795763659292</v>
+        <v>4.98804161906678</v>
       </c>
       <c r="G35" t="n">
         <v>17</v>
       </c>
       <c r="H35" t="n">
-        <v>12.6020423634071</v>
+        <v>12.0119583809332</v>
       </c>
     </row>
     <row r="36">
@@ -1503,13 +1503,13 @@
         <v>-4.78359630973114</v>
       </c>
       <c r="F36" t="n">
-        <v>5.08798336758948</v>
+        <v>5.7706496723595</v>
       </c>
       <c r="G36" t="n">
         <v>16</v>
       </c>
       <c r="H36" t="n">
-        <v>10.9120166324105</v>
+        <v>10.2293503276405</v>
       </c>
     </row>
     <row r="37">
@@ -1529,13 +1529,13 @@
         <v>-23.227984850148</v>
       </c>
       <c r="F37" t="n">
-        <v>24.5875041732528</v>
+        <v>27.8864655504446</v>
       </c>
       <c r="G37" t="n">
         <v>15</v>
       </c>
       <c r="H37" t="n">
-        <v>-9.5875041732528</v>
+        <v>-12.8864655504446</v>
       </c>
     </row>
     <row r="38">
@@ -1555,13 +1555,13 @@
         <v>-31.1470107650759</v>
       </c>
       <c r="F38" t="n">
-        <v>29.7131295107978</v>
+        <v>33.6998077015128</v>
       </c>
       <c r="G38" t="n">
         <v>14</v>
       </c>
       <c r="H38" t="n">
-        <v>-15.7131295107978</v>
+        <v>-19.6998077015128</v>
       </c>
     </row>
     <row r="39">
@@ -1581,13 +1581,13 @@
         <v>-34.3722803696653</v>
       </c>
       <c r="F39" t="n">
-        <v>24.4140431171777</v>
+        <v>27.6897308298118</v>
       </c>
       <c r="G39" t="n">
         <v>13</v>
       </c>
       <c r="H39" t="n">
-        <v>-11.4140431171777</v>
+        <v>-14.6897308298118</v>
       </c>
     </row>
     <row r="40">
@@ -1629,13 +1629,13 @@
         <v>-26.2670186083408</v>
       </c>
       <c r="F41" t="n">
-        <v>16.9842061939341</v>
+        <v>19.2630157819768</v>
       </c>
       <c r="G41" t="n">
         <v>11</v>
       </c>
       <c r="H41" t="n">
-        <v>-5.9842061939341</v>
+        <v>-8.2630157819768</v>
       </c>
     </row>
     <row r="42">
@@ -1655,13 +1655,13 @@
         <v>-83.6751164571433</v>
       </c>
       <c r="F42" t="n">
-        <v>46.2654276758687</v>
+        <v>52.4729653717031</v>
       </c>
       <c r="G42" t="n">
         <v>10</v>
       </c>
       <c r="H42" t="n">
-        <v>-36.2654276758687</v>
+        <v>-42.4729653717031</v>
       </c>
     </row>
     <row r="43">
@@ -1725,13 +1725,13 @@
         <v>-17.1623788713976</v>
       </c>
       <c r="F45" t="n">
-        <v>1.03119809319374</v>
+        <v>1.16955628757204</v>
       </c>
       <c r="G45" t="n">
         <v>7</v>
       </c>
       <c r="H45" t="n">
-        <v>5.96880190680626</v>
+        <v>5.83044371242796</v>
       </c>
     </row>
     <row r="46">
@@ -1751,13 +1751,13 @@
         <v>-29.0633479363489</v>
       </c>
       <c r="F46" t="n">
-        <v>7.4385364517734</v>
+        <v>8.43658181190103</v>
       </c>
       <c r="G46" t="n">
         <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.4385364517734</v>
+        <v>-2.43658181190103</v>
       </c>
     </row>
     <row r="47">
@@ -1777,13 +1777,13 @@
         <v>-45.8599513351417</v>
       </c>
       <c r="F47" t="n">
-        <v>3.80873915452093</v>
+        <v>4.31976635264669</v>
       </c>
       <c r="G47" t="n">
         <v>5</v>
       </c>
       <c r="H47" t="n">
-        <v>1.19126084547907</v>
+        <v>0.68023364735331</v>
       </c>
     </row>
     <row r="48">
@@ -1803,13 +1803,13 @@
         <v>-31.2117319593885</v>
       </c>
       <c r="F48" t="n">
-        <v>0.886196036481758</v>
+        <v>1.00509897499774</v>
       </c>
       <c r="G48" t="n">
         <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>3.11380396351824</v>
+        <v>2.99490102500226</v>
       </c>
     </row>
     <row r="49">
@@ -1851,13 +1851,13 @@
         <v>-47.3049644973489</v>
       </c>
       <c r="F50" t="n">
-        <v>2.89472438896276</v>
+        <v>3.2831161463983</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.89472438896276</v>
+        <v>-1.2831161463983</v>
       </c>
     </row>
     <row r="51">
@@ -1877,13 +1877,13 @@
         <v>-36.6761935964735</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.34164714660656</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1.34164714660656</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1925,13 +1925,13 @@
         <v>-54.2163953506715</v>
       </c>
       <c r="F53" t="n">
-        <v>1.55075517758024</v>
+        <v>1.75882352808337</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.55075517758024</v>
+        <v>-1.75882352808337</v>
       </c>
     </row>
     <row r="54">
@@ -1973,13 +1973,13 @@
         <v>-70.3108728049722</v>
       </c>
       <c r="F55" t="n">
-        <v>3.89562494997936</v>
+        <v>4.41830981296708</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-3.89562494997936</v>
+        <v>-4.41830981296708</v>
       </c>
     </row>
     <row r="56">
@@ -1999,13 +1999,13 @@
         <v>-59.6896813978408</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.319258260812212</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.319258260812212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
